--- a/data/transformed/estadoObra_filtrado.xlsx
+++ b/data/transformed/estadoObra_filtrado.xlsx
@@ -16,10 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -49,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,158 +413,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>descSucursal</t>
+          <t>SUC</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>descProyecto</t>
+          <t>HC</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>hc</t>
+          <t>Nombre</t>
         </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Actividad</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>tipoRestriccion</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>nomAcuerdoServ</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Responsable</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>fechaRegistro</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>FechaCompromisoInicial</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>FecLegalizacion</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>FecInicioFabricacion</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BOGOTA </t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>LOIRA CIUDAD LA SALLE</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>2848251000</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>ZS LOCALES - Afinados sobre pisos y escaleras</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Contratos</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>PISOS Y ENCHAPES</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Karen Valentina Sanchez Guzman</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="n">
-        <v>46086</v>
-      </c>
-      <c r="I2" s="1" t="n">
-        <v>45475</v>
-      </c>
-      <c r="J2" s="1" t="n">
-        <v>45427</v>
-      </c>
-      <c r="K2" s="1" t="n">
-        <v>45350</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BOGOTA </t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>METROPOLI 30</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>2847101000</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>T2 Red de T.V</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Contratos</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>INSTALACIONES ELÉCTRICAS</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>SILVIO ANDRES VELANDIA</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="n">
-        <v>46098</v>
-      </c>
-      <c r="I3" s="1" t="n">
-        <v>45973</v>
-      </c>
-      <c r="J3" s="1" t="n">
-        <v>46084</v>
-      </c>
-      <c r="K3" s="1" t="n">
-        <v>45745</v>
       </c>
     </row>
   </sheetData>
